--- a/샘플_타증권사_보유종목.xlsx
+++ b/샘플_타증권사_보유종목.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\주식대시보드\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\asset-dashboard-clean\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -22,82 +22,82 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <x:si>
+    <x:t>대시보드의 전체 보유 종목 &gt; 파일 가져오기에서 XLSX를 선택하세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>증권사 → 계좌명 → 종목코드 → 종목명 → 보유수량 → 평균매입가 → 현재가 → 통화 → 거래소</x:t>
+  </x:si>
+  <x:si>
     <x:t>NH투자증권(나무)</x:t>
   </x:si>
   <x:si>
+    <x:t>종목코드, 보유수량</x:t>
+  </x:si>
+  <x:si>
     <x:t>KODEX 미국나스닥100</x:t>
   </x:si>
   <x:si>
     <x:t>증권사</x:t>
   </x:si>
   <x:si>
+    <x:t>종목명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현재가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거래소</x:t>
+  </x:si>
+  <x:si>
     <x:t>계좌명</x:t>
   </x:si>
   <x:si>
-    <x:t>거래소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>현재가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종목명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종목코드, 보유수량</x:t>
+    <x:t>연금저축</x:t>
+  </x:si>
+  <x:si>
+    <x:t>005930</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평균매입가</x:t>
   </x:si>
   <x:si>
     <x:t>삼성전자</x:t>
   </x:si>
   <x:si>
+    <x:t>일반 주식계좌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가져오기</x:t>
+  </x:si>
+  <x:si>
     <x:t>종목코드</x:t>
   </x:si>
   <x:si>
-    <x:t>평균매입가</x:t>
-  </x:si>
-  <x:si>
     <x:t>보유수량</x:t>
   </x:si>
   <x:si>
+    <x:t>필수 항목</x:t>
+  </x:si>
+  <x:si>
     <x:t>입력 순서</x:t>
   </x:si>
   <x:si>
-    <x:t>연금저축</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반 주식계좌</x:t>
-  </x:si>
-  <x:si>
     <x:t>379810</x:t>
   </x:si>
   <x:si>
-    <x:t>가져오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필수 항목</x:t>
-  </x:si>
-  <x:si>
     <x:t>기타 증권사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>005930</x:t>
-  </x:si>
-  <x:si>
-    <x:t>증권사 → 계좌명 → 종목코드 → 종목명 → 보유수량 → 평균매입가 → 현재가 → 통화 → 거래소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대시보드의 전체 보유 종목 &gt; 파일 가져오기에서 XLSX를 선택하세요.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -237,7 +237,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -320,7 +319,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -355,7 +353,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -400,7 +397,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -444,7 +440,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -529,7 +524,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -550,7 +544,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -581,7 +574,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -844,45 +836,45 @@
   <x:sheetData>
     <x:row r="1" spans="1:9">
       <x:c r="A1" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:9">
       <x:c r="A2" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E2" s="3">
         <x:v>1569</x:v>
@@ -894,24 +886,24 @@
         <x:v>28185</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
       <x:c r="A3" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E3" s="3">
         <x:v>831</x:v>
@@ -923,24 +915,24 @@
         <x:v>28185</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
       <x:c r="A4" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E4" s="3">
         <x:v>10</x:v>
@@ -952,14 +944,14 @@
         <x:v>75000</x:v>
       </x:c>
       <x:c r="H4" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I4" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -968,34 +960,38 @@
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet2"/>
   <x:dimension ref="A1:B3"/>
-  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="13.55000000000000071054"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9.99609375" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="83.40234375" bestFit="1" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
--- a/샘플_타증권사_보유종목.xlsx
+++ b/샘플_타증권사_보유종목.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="보유종목" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,12 +45,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="006366F1"/>
-        <bgColor rgb="006366F1"/>
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -60,31 +60,51 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00334155"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00334155"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00334155"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -452,21 +472,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>소유자</t>
@@ -513,7 +533,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>아빠</t>
@@ -534,18 +554,18 @@
           <t>005930</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>72000</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>78500</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -554,7 +574,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>아빠</t>
@@ -575,18 +595,18 @@
           <t>QQQM</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Invesco NASDAQ 100 ETF</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <v>185.5</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>210.2</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -595,83 +615,206 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>아빠</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>한국투자</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>한투공모주</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>267260</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>HD현대일렉트릭</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>240000</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>285000</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>엄마</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>키움증권</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>키움위탁계좌</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>000660</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F5" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G5" s="4" t="n">
         <v>165000</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H5" s="4" t="n">
         <v>192000</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>엄마</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>미래에셋</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>미래에셋ISA</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>379810</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>KODEX 미국나스닥100</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>15200</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>17800</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>자녀</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>토스증권</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>토스자녀계좌</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>SCHD</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Schwab US Dividend Equity ETF</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G7" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>82.5</v>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>자녀</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>토스증권</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>토스자녀계좌</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Apple Inc</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>195</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>224.5</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
